--- a/src/nodes/LPC/compressor_stage_parameters.xlsx
+++ b/src/nodes/LPC/compressor_stage_parameters.xlsx
@@ -653,10 +653,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="D3">
         <v>62.101636171585326</v>
@@ -665,16 +665,16 @@
         <v>35.223425172497393</v>
       </c>
       <c r="F3">
-        <v>38.314355165736856</v>
+        <v>39.570563531826586</v>
       </c>
       <c r="G3">
-        <v>17.815527842904959</v>
+        <v>31.880418245198349</v>
       </c>
       <c r="H3">
-        <v>1.552112837535145</v>
+        <v>1.4234743347562517</v>
       </c>
       <c r="I3">
-        <v>-0.057201576751886855</v>
+        <v>-2.2378479399495843</v>
       </c>
       <c r="J3">
         <v>0.32837094704008479</v>
@@ -683,34 +683,34 @@
         <v>0.30041042805014695</v>
       </c>
       <c r="L3">
-        <v>24.057869291821444</v>
+        <v>24.368951636451822</v>
       </c>
       <c r="M3">
-        <v>25.234337523583772</v>
+        <v>30.8368819415207</v>
       </c>
       <c r="N3">
-        <v>6.2051334435797338</v>
+        <v>6.3875772854312185</v>
       </c>
       <c r="O3">
-        <v>5.3912623550494585</v>
+        <v>8.81316040978869</v>
       </c>
       <c r="P3">
-        <v>12.028934645910722</v>
+        <v>12.184475818225911</v>
       </c>
       <c r="Q3">
-        <v>12.617168761791886</v>
+        <v>15.418440970760351</v>
       </c>
       <c r="R3">
-        <v>34.990725277626616</v>
+        <v>35.017627947162921</v>
       </c>
       <c r="S3">
-        <v>44.471526840404749</v>
+        <v>45.09215268617551</v>
       </c>
       <c r="T3">
-        <v>148.9922203919802</v>
+        <v>147.11846872613441</v>
       </c>
       <c r="U3">
-        <v>80.6265426932178</v>
+        <v>66.242715772038935</v>
       </c>
       <c r="V3">
         <v>0.92630385487528355</v>
@@ -719,25 +719,25 @@
         <v>0.92044063647490815</v>
       </c>
       <c r="X3">
-        <v>0.64908603656970831</v>
+        <v>0.65454225405358279</v>
       </c>
       <c r="Y3">
-        <v>0.53238624767210829</v>
+        <v>0.63332512888312742</v>
       </c>
       <c r="Z3">
-        <v>0.16417639268189552</v>
+        <v>0.16196124355071134</v>
       </c>
       <c r="AA3">
-        <v>0.10615365540537027</v>
+        <v>0.08479213628487263</v>
       </c>
       <c r="AB3">
-        <v>7.8665314191210136</v>
+        <v>7.9988982651772194</v>
       </c>
       <c r="AC3">
-        <v>9.6387539135622369</v>
+        <v>12.351109455017499</v>
       </c>
       <c r="AD3">
-        <v>76.991204940544009</v>
+        <v>78.40133526227379</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -745,10 +745,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="C4">
-        <v>90</v>
+        <v>812</v>
       </c>
       <c r="D4">
         <v>66.350378352099824</v>
@@ -757,16 +757,16 @@
         <v>44.77951176409146</v>
       </c>
       <c r="F4">
-        <v>40.517139600808292</v>
+        <v>16.043699573474424</v>
       </c>
       <c r="G4">
-        <v>25.744939923793329</v>
+        <v>2.8535031935238906</v>
       </c>
       <c r="H4">
-        <v>1.5939697993127933</v>
+        <v>7.8390084762306165</v>
       </c>
       <c r="I4">
-        <v>-0.65162009538168642</v>
+        <v>34.232049806111895</v>
       </c>
       <c r="J4">
         <v>0.2626315273608727</v>
@@ -775,34 +775,34 @@
         <v>0.32017704096510424</v>
       </c>
       <c r="L4">
-        <v>61.235290267883613</v>
+        <v>48.71399174055027</v>
       </c>
       <c r="M4">
-        <v>48.797533061778</v>
+        <v>2.249021633546767</v>
       </c>
       <c r="N4">
-        <v>12.567425726554145</v>
+        <v>6.2911658761386189</v>
       </c>
       <c r="O4">
-        <v>11.846616179623734</v>
+        <v>0.18177465288608188</v>
       </c>
       <c r="P4">
-        <v>30.617645133941807</v>
+        <v>24.356995870275135</v>
       </c>
       <c r="Q4">
-        <v>24.398766530889</v>
+        <v>1.1245108167733835</v>
       </c>
       <c r="R4">
-        <v>55.634016912175987</v>
+        <v>55.618406325427138</v>
       </c>
       <c r="S4">
-        <v>43.04039882426946</v>
+        <v>54.649813011647431</v>
       </c>
       <c r="T4">
-        <v>65.137969160404751</v>
+        <v>80.440147984535258</v>
       </c>
       <c r="U4">
-        <v>54.201351773854938</v>
+        <v>1140.8701973851164</v>
       </c>
       <c r="V4">
         <v>0.92787234042553191</v>
@@ -811,25 +811,25 @@
         <v>0.9245585874799358</v>
       </c>
       <c r="X4">
-        <v>0.86289075604260634</v>
+        <v>0.713573363583463</v>
       </c>
       <c r="Y4">
-        <v>0.75055521941319792</v>
+        <v>0.58763027601947548</v>
       </c>
       <c r="Z4">
-        <v>0.22385090640910466</v>
+        <v>0.35436401891558716</v>
       </c>
       <c r="AA4">
-        <v>0.22850038883356177</v>
+        <v>1.1878892553183527</v>
       </c>
       <c r="AB4">
-        <v>6.2910304853910537</v>
+        <v>3.4989201860193679</v>
       </c>
       <c r="AC4">
-        <v>6.2189887278084655</v>
+        <v>-0.33180398672282529</v>
       </c>
       <c r="AD4">
-        <v>71.591061407489278</v>
+        <v>-10.141965939263486</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -837,10 +837,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="C5">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="D5">
         <v>74.877641662795867</v>
@@ -849,16 +849,16 @@
         <v>64.290738572725715</v>
       </c>
       <c r="F5">
-        <v>44.952010732227293</v>
+        <v>19.492464830788823</v>
       </c>
       <c r="G5">
-        <v>35.326690075160705</v>
+        <v>13.479921212890268</v>
       </c>
       <c r="H5">
-        <v>1.6643099186836874</v>
+        <v>7.1034085879848305</v>
       </c>
       <c r="I5">
-        <v>-0.45027156266682522</v>
+        <v>6.9234262495628034</v>
       </c>
       <c r="J5">
         <v>0.26301454474940439</v>
@@ -867,34 +867,34 @@
         <v>0.30861065303165713</v>
       </c>
       <c r="L5">
-        <v>60.671404821319882</v>
+        <v>49.512561509962289</v>
       </c>
       <c r="M5">
-        <v>41.701551685451662</v>
+        <v>28.867343831320927</v>
       </c>
       <c r="N5">
-        <v>12.364094032558935</v>
+        <v>6.6443493905024855</v>
       </c>
       <c r="O5">
-        <v>9.53982471937949</v>
+        <v>4.0793146774783882</v>
       </c>
       <c r="P5">
-        <v>30.335702410659941</v>
+        <v>24.756280754981145</v>
       </c>
       <c r="Q5">
-        <v>20.850775842725831</v>
+        <v>14.433671915660463</v>
       </c>
       <c r="R5">
-        <v>55.521119247196815</v>
+        <v>55.38079626081916</v>
       </c>
       <c r="S5">
-        <v>39.383722360825089</v>
+        <v>40.340316245989349</v>
       </c>
       <c r="T5">
-        <v>74.126660191018175</v>
+        <v>89.404156812362984</v>
       </c>
       <c r="U5">
-        <v>90.3124021078891</v>
+        <v>128.963691092365</v>
       </c>
       <c r="V5">
         <v>0.9600000000000003</v>
@@ -903,25 +903,25 @@
         <v>0.95833333333333315</v>
       </c>
       <c r="X5">
-        <v>0.84155540991959177</v>
+        <v>0.70497568969015245</v>
       </c>
       <c r="Y5">
-        <v>0.78680946017629927</v>
+        <v>0.66950439882597323</v>
       </c>
       <c r="Z5">
-        <v>0.21385761661194383</v>
+        <v>0.32024984053866612</v>
       </c>
       <c r="AA5">
-        <v>0.24472644280334718</v>
+        <v>0.4374753478626609</v>
       </c>
       <c r="AB5">
-        <v>6.6577918513178487</v>
+        <v>4.0170692886518875</v>
       </c>
       <c r="AC5">
-        <v>6.1124994214458805</v>
+        <v>2.6061417796117081</v>
       </c>
       <c r="AD5">
-        <v>71.401749031727618</v>
+        <v>52.1760844373393</v>
       </c>
     </row>
   </sheetData>
@@ -1243,10 +1243,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="D3">
         <v>72.070923318547244</v>
@@ -1255,16 +1255,16 @@
         <v>38.993078292681723</v>
       </c>
       <c r="F3">
-        <v>45.106015042705039</v>
+        <v>46.58490078181012</v>
       </c>
       <c r="G3">
-        <v>20.923173871910674</v>
+        <v>37.441469033945424</v>
       </c>
       <c r="H3">
-        <v>1.4945295128771974</v>
+        <v>1.367719052150937</v>
       </c>
       <c r="I3">
-        <v>-0.34092215987486241</v>
+        <v>-2.396397677577129</v>
       </c>
       <c r="J3">
         <v>0.35408390267839268</v>
@@ -1273,34 +1273,34 @@
         <v>0.29205238380960541</v>
       </c>
       <c r="L3">
-        <v>11.201552086696106</v>
+        <v>11.450158543303239</v>
       </c>
       <c r="M3">
-        <v>25.666033663547019</v>
+        <v>31.143348474116351</v>
       </c>
       <c r="N3">
-        <v>3.1377733728308081</v>
+        <v>3.2595693687116807</v>
       </c>
       <c r="O3">
-        <v>5.49084944863093</v>
+        <v>8.9126887414979983</v>
       </c>
       <c r="P3">
-        <v>5.6007760433480529</v>
+        <v>5.7250792716516195</v>
       </c>
       <c r="Q3">
-        <v>12.833016831773509</v>
+        <v>15.571674237058176</v>
       </c>
       <c r="R3">
-        <v>25.495045990286428</v>
+        <v>25.492538757863734</v>
       </c>
       <c r="S3">
-        <v>48.704684319367388</v>
+        <v>49.387866206949781</v>
       </c>
       <c r="T3">
-        <v>369.22949191217407</v>
+        <v>361.238596974425</v>
       </c>
       <c r="U3">
-        <v>87.778599121691869</v>
+        <v>72.628058857940459</v>
       </c>
       <c r="V3">
         <v>0.92630385487528355</v>
@@ -1309,25 +1309,25 @@
         <v>0.92044063647490815</v>
       </c>
       <c r="X3">
-        <v>0.50089868524824777</v>
+        <v>0.50498226661677492</v>
       </c>
       <c r="Y3">
-        <v>0.49414827699855124</v>
+        <v>0.59576562722267623</v>
       </c>
       <c r="Z3">
-        <v>0.13343551091124095</v>
+        <v>0.13112409902690783</v>
       </c>
       <c r="AA3">
-        <v>0.083090167923328226</v>
+        <v>0.066841814474827912</v>
       </c>
       <c r="AB3">
-        <v>8.7572368298685319</v>
+        <v>8.9534841923303876</v>
       </c>
       <c r="AC3">
-        <v>11.373319568539928</v>
+        <v>14.37130315520084</v>
       </c>
       <c r="AD3">
-        <v>76.424342243107773</v>
+        <v>77.513493937542123</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -1335,10 +1335,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="C4">
-        <v>90</v>
+        <v>812</v>
       </c>
       <c r="D4">
         <v>77.018428520762043</v>
@@ -1347,16 +1347,16 @@
         <v>49.579384700183112</v>
       </c>
       <c r="F4">
-        <v>47.688630388349395</v>
+        <v>18.883417402098083</v>
       </c>
       <c r="G4">
-        <v>30.512570429489795</v>
+        <v>3.3819351461257159</v>
       </c>
       <c r="H4">
-        <v>1.5375676494358959</v>
+        <v>7.6965691485753975</v>
       </c>
       <c r="I4">
-        <v>-0.937790228558914</v>
+        <v>31.650159271224023</v>
       </c>
       <c r="J4">
         <v>0.33453885199695405</v>
@@ -1365,34 +1365,34 @@
         <v>0.31028531713250546</v>
       </c>
       <c r="L4">
-        <v>23.579144370450081</v>
+        <v>13.439313036690209</v>
       </c>
       <c r="M4">
-        <v>51.034459841075119</v>
+        <v>6.5550970933002732</v>
       </c>
       <c r="N4">
-        <v>6.2070422585276077</v>
+        <v>2.2262124239072394</v>
       </c>
       <c r="O4">
-        <v>12.42263081080967</v>
+        <v>0.53121756281776444</v>
       </c>
       <c r="P4">
-        <v>11.78957218522504</v>
+        <v>6.7196565183451042</v>
       </c>
       <c r="Q4">
-        <v>25.517229920537559</v>
+        <v>3.2775485466501366</v>
       </c>
       <c r="R4">
-        <v>32.148044074825549</v>
+        <v>33.237129907085112</v>
       </c>
       <c r="S4">
-        <v>46.970606893720628</v>
+        <v>57.318875019616137</v>
       </c>
       <c r="T4">
-        <v>188.47695294817783</v>
+        <v>329.10635282890519</v>
       </c>
       <c r="U4">
-        <v>57.545727251945067</v>
+        <v>433.5922580085969</v>
       </c>
       <c r="V4">
         <v>0.92787234042553191</v>
@@ -1401,25 +1401,25 @@
         <v>0.9245585874799358</v>
       </c>
       <c r="X4">
-        <v>0.68410365530197437</v>
+        <v>0.57944694334692226</v>
       </c>
       <c r="Y4">
-        <v>0.73240128116784819</v>
+        <v>0.56068906267889951</v>
       </c>
       <c r="Z4">
-        <v>0.19676936924152361</v>
+        <v>0.3460169325714153</v>
       </c>
       <c r="AA4">
-        <v>0.18591044842096449</v>
+        <v>0.93127876742509852</v>
       </c>
       <c r="AB4">
-        <v>7.0863377566752792</v>
+        <v>3.1384044253585421</v>
       </c>
       <c r="AC4">
-        <v>7.2262447049319309</v>
+        <v>0.15918631843730569</v>
       </c>
       <c r="AD4">
-        <v>73.268131068607019</v>
+        <v>17.947364166952173</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -1427,10 +1427,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="C5">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="D5">
         <v>87.026662430162162</v>
@@ -1439,16 +1439,16 @@
         <v>71.24492410104699</v>
       </c>
       <c r="F5">
-        <v>53.975684604072065</v>
+        <v>23.405385359287887</v>
       </c>
       <c r="G5">
-        <v>43.2855267781047</v>
+        <v>16.516845744276797</v>
       </c>
       <c r="H5">
-        <v>1.5308271709997285</v>
+        <v>6.7955810269993737</v>
       </c>
       <c r="I5">
-        <v>-0.88517632774397115</v>
+        <v>5.7836758307399379</v>
       </c>
       <c r="J5">
         <v>0.34105752463448857</v>
@@ -1457,34 +1457,34 @@
         <v>0.29692319017481894</v>
       </c>
       <c r="L5">
-        <v>20.462709092793681</v>
+        <v>11.786431750959094</v>
       </c>
       <c r="M5">
-        <v>45.597935106927665</v>
+        <v>33.109389273564041</v>
       </c>
       <c r="N5">
-        <v>5.4962146004349348</v>
+        <v>2.0846911145999942</v>
       </c>
       <c r="O5">
-        <v>10.553188212608378</v>
+        <v>4.7334945377286637</v>
       </c>
       <c r="P5">
-        <v>10.23135454639684</v>
+        <v>5.8932158754795472</v>
       </c>
       <c r="Q5">
-        <v>22.798967553463832</v>
+        <v>16.55469463678202</v>
       </c>
       <c r="R5">
-        <v>29.736097736793823</v>
+        <v>30.662712921876178</v>
       </c>
       <c r="S5">
-        <v>44.292625571735094</v>
+        <v>44.717204813537194</v>
       </c>
       <c r="T5">
-        <v>244.97534939330566</v>
+        <v>423.79774809926522</v>
       </c>
       <c r="U5">
-        <v>91.929177540810755</v>
+        <v>125.021580039852</v>
       </c>
       <c r="V5">
         <v>0.9600000000000003</v>
@@ -1493,25 +1493,25 @@
         <v>0.95833333333333315</v>
       </c>
       <c r="X5">
-        <v>0.63776400150834633</v>
+        <v>0.54648509374095178</v>
       </c>
       <c r="Y5">
-        <v>0.77029128334699759</v>
+        <v>0.64187900046885993</v>
       </c>
       <c r="Z5">
-        <v>0.18139353747192932</v>
+        <v>0.3031937209129027</v>
       </c>
       <c r="AA5">
-        <v>0.1948813273638447</v>
+        <v>0.33393715569806792</v>
       </c>
       <c r="AB5">
-        <v>8.0348539965318668</v>
+        <v>3.9070443341879382</v>
       </c>
       <c r="AC5">
-        <v>7.2634058951720837</v>
+        <v>3.6012762427520668</v>
       </c>
       <c r="AD5">
-        <v>74.089661230379747</v>
+        <v>56.463472781425104</v>
       </c>
     </row>
   </sheetData>
@@ -1833,10 +1833,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="D3">
         <v>80.732127023060926</v>
@@ -1845,16 +1845,16 @@
         <v>42.268110206996866</v>
       </c>
       <c r="F3">
-        <v>51.001098287682318</v>
+        <v>52.67326544465552</v>
       </c>
       <c r="G3">
-        <v>23.625508765617546</v>
+        <v>42.277226212157707</v>
       </c>
       <c r="H3">
-        <v>1.4573719847989619</v>
+        <v>1.3317411281386771</v>
       </c>
       <c r="I3">
-        <v>-0.52728042533097763</v>
+        <v>-2.5005390612143694</v>
       </c>
       <c r="J3">
         <v>0.36580980950748471</v>
@@ -1863,34 +1863,34 @@
         <v>0.28611938764440287</v>
       </c>
       <c r="L3">
-        <v>5.9984433192605948</v>
+        <v>6.2170194160735885</v>
       </c>
       <c r="M3">
-        <v>25.568747093101436</v>
+        <v>30.920498442534008</v>
       </c>
       <c r="N3">
-        <v>1.7440561926716365</v>
+        <v>1.8370014328243456</v>
       </c>
       <c r="O3">
-        <v>5.4694153307266422</v>
+        <v>8.84790804427582</v>
       </c>
       <c r="P3">
-        <v>2.9992216596302974</v>
+        <v>3.1085097080367943</v>
       </c>
       <c r="Q3">
-        <v>12.784373546550718</v>
+        <v>15.460249221267004</v>
       </c>
       <c r="R3">
-        <v>20.839929779299005</v>
+        <v>20.823586971045216</v>
       </c>
       <c r="S3">
-        <v>51.860111856214715</v>
+        <v>52.562728895047613</v>
       </c>
       <c r="T3">
-        <v>771.48737502624169</v>
+        <v>744.38888496683978</v>
       </c>
       <c r="U3">
-        <v>95.50710907822058</v>
+        <v>79.2815168328039</v>
       </c>
       <c r="V3">
         <v>0.92630385487528355</v>
@@ -1899,25 +1899,25 @@
         <v>0.92044063647490815</v>
       </c>
       <c r="X3">
-        <v>0.40513469803720026</v>
+        <v>0.40840514523388238</v>
       </c>
       <c r="Y3">
-        <v>0.46301641956870521</v>
+        <v>0.56400484564218489</v>
       </c>
       <c r="Z3">
-        <v>0.11666598346405271</v>
+        <v>0.11428290965851791</v>
       </c>
       <c r="AA3">
-        <v>0.0691963980953599</v>
+        <v>0.055672811796179486</v>
       </c>
       <c r="AB3">
-        <v>8.7682692149890613</v>
+        <v>9.0103622321108787</v>
       </c>
       <c r="AC3">
-        <v>12.814037783589644</v>
+        <v>16.133109656381112</v>
       </c>
       <c r="AD3">
-        <v>74.249542199822358</v>
+        <v>75.268388251426444</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -1925,10 +1925,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="C4">
-        <v>90</v>
+        <v>812</v>
       </c>
       <c r="D4">
         <v>86.25549185772978</v>
@@ -1937,16 +1937,16 @@
         <v>53.735414116909745</v>
       </c>
       <c r="F4">
-        <v>53.914211867843157</v>
+        <v>21.348580538273467</v>
       </c>
       <c r="G4">
-        <v>34.6297457373363</v>
+        <v>3.8382723107885059</v>
       </c>
       <c r="H4">
-        <v>1.4996639508133298</v>
+        <v>7.6008462486641717</v>
       </c>
       <c r="I4">
-        <v>-1.120718404598728</v>
+        <v>29.999740616287042</v>
       </c>
       <c r="J4">
         <v>0.3583516442120841</v>
@@ -1955,34 +1955,34 @@
         <v>0.30312329373741004</v>
       </c>
       <c r="L4">
-        <v>11.424819355591362</v>
+        <v>2.5395833659661795</v>
       </c>
       <c r="M4">
-        <v>51.926496171097035</v>
+        <v>8.8904876516877849</v>
       </c>
       <c r="N4">
-        <v>3.2368084251421156</v>
+        <v>0.45275473336777555</v>
       </c>
       <c r="O4">
-        <v>12.635798203134131</v>
+        <v>0.7202487046106455</v>
       </c>
       <c r="P4">
-        <v>5.712409677795681</v>
+        <v>1.2697916829830898</v>
       </c>
       <c r="Q4">
-        <v>25.963248085548518</v>
+        <v>4.4452438258438924</v>
       </c>
       <c r="R4">
-        <v>23.348576641304405</v>
+        <v>25.007140944342655</v>
       </c>
       <c r="S4">
-        <v>49.81592256062617</v>
+        <v>59.418377321807313</v>
       </c>
       <c r="T4">
-        <v>433.2911093694313</v>
+        <v>1946.1775848473944</v>
       </c>
       <c r="U4">
-        <v>61.370586121148648</v>
+        <v>346.65177500420646</v>
       </c>
       <c r="V4">
         <v>0.92787234042553191</v>
@@ -1991,25 +1991,25 @@
         <v>0.9245585874799358</v>
       </c>
       <c r="X4">
-        <v>0.54167798150024993</v>
+        <v>0.46093455069538675</v>
       </c>
       <c r="Y4">
-        <v>0.71283776607469274</v>
+        <v>0.53605747849446173</v>
       </c>
       <c r="Z4">
-        <v>0.16660194482486745</v>
+        <v>0.31418999650930152</v>
       </c>
       <c r="AA4">
-        <v>0.15848385945784535</v>
+        <v>0.77483172571187831</v>
       </c>
       <c r="AB4">
-        <v>7.9063716047522057</v>
+        <v>2.9303094354546197</v>
       </c>
       <c r="AC4">
-        <v>8.0877937395184372</v>
+        <v>0.52759000465004147</v>
       </c>
       <c r="AD4">
-        <v>73.175106596474478</v>
+        <v>27.2150064707259</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -2017,10 +2017,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="C5">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="D5">
         <v>97.340934161634621</v>
@@ -2029,16 +2029,16 @@
         <v>77.148886287270855</v>
       </c>
       <c r="F5">
-        <v>61.690928488780536</v>
+        <v>26.750933592480056</v>
       </c>
       <c r="G5">
-        <v>49.990924809873881</v>
+        <v>19.075484466925563</v>
       </c>
       <c r="H5">
-        <v>1.4447021039461905</v>
+        <v>6.5969660764473375</v>
       </c>
       <c r="I5">
-        <v>-1.1418554177240932</v>
+        <v>5.1109995949299636</v>
       </c>
       <c r="J5">
         <v>0.36363810977071787</v>
@@ -2047,34 +2047,34 @@
         <v>0.28929783006793691</v>
       </c>
       <c r="L5">
-        <v>9.4299878405756026</v>
+        <v>1.9124066779520892</v>
       </c>
       <c r="M5">
-        <v>47.362597687484289</v>
+        <v>35.134259367810195</v>
       </c>
       <c r="N5">
-        <v>2.7298791580074928</v>
+        <v>0.36456196788512429</v>
       </c>
       <c r="O5">
-        <v>11.02964273341313</v>
+        <v>5.0541594263930962</v>
       </c>
       <c r="P5">
-        <v>4.7149939202878013</v>
+        <v>0.95620333897604459</v>
       </c>
       <c r="Q5">
-        <v>23.681298843742145</v>
+        <v>17.567129683905097</v>
       </c>
       <c r="R5">
-        <v>21.195830352360776</v>
+        <v>22.589303743550168</v>
       </c>
       <c r="S5">
-        <v>47.699428855702543</v>
+        <v>47.838114708519555</v>
       </c>
       <c r="T5">
-        <v>592.10304414891607</v>
+        <v>2916.4736079039421</v>
       </c>
       <c r="U5">
-        <v>96.040209477683291</v>
+        <v>127.80484964567165</v>
       </c>
       <c r="V5">
         <v>0.9600000000000003</v>
@@ -2083,25 +2083,25 @@
         <v>0.95833333333333315</v>
       </c>
       <c r="X5">
-        <v>0.48903588074408927</v>
+        <v>0.420091851561748</v>
       </c>
       <c r="Y5">
-        <v>0.74930007403975885</v>
+        <v>0.61441427422239636</v>
       </c>
       <c r="Z5">
-        <v>0.15033802129102689</v>
+        <v>0.27030171379267443</v>
       </c>
       <c r="AA5">
-        <v>0.16403739193524763</v>
+        <v>0.27325717200113581</v>
       </c>
       <c r="AB5">
-        <v>9.3076709836405609</v>
+        <v>3.8532172343546227</v>
       </c>
       <c r="AC5">
-        <v>8.2467095970514972</v>
+        <v>4.4160483118902212</v>
       </c>
       <c r="AD5">
-        <v>74.394290427990867</v>
+        <v>55.084464230865663</v>
       </c>
     </row>
   </sheetData>
